--- a/employee_information_forms/003_screening_checklist_for_visitors_and_employees--employee_information_forms.xlsx
+++ b/employee_information_forms/003_screening_checklist_for_visitors_and_employees--employee_information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'name',_'label':_'name',_'type':_'text',_'required':_true}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'name', 'label': 'Name', 'type': 'text', 'required': True}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'contact_location',_'label':_'contact_location',_'type':_'text',_'required':_true}</t>
+          <t>contact_location</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'contact_location', 'label': 'Contact Location', 'type': 'text', 'required': True}</t>
+          <t>Contact Location</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'date_of_contact',_'label':_'date_of_contact',_'type':_'date',_'required':_true}</t>
+          <t>date_of_contact</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'date_of_contact', 'label': 'Date of Contact', 'type': 'date', 'required': True}</t>
+          <t>Date of Contact</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'contact_type',_'label':_'contact_type',_'type':_'select_one',_'options':_[{'name':_'direct_contact',_'label':_'direct_contact'},_{'name':_'indirect_contact',_'label':_'indirect_contact'},_{'name':_'no_contact',_'label':_'no_contact'}],_'required':_true}</t>
+          <t>contact_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'contact_type', 'label': 'Contact Type', 'type': 'select_one', 'options': [{'name': 'Direct Contact', 'label': 'Direct Contact'}, {'name': 'Indirect Contact', 'label': 'Indirect Contact'}, {'name': 'No Contact', 'label': 'No Contact'}], 'required': True}</t>
+          <t>Contact Type</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'previously_treated_doctor',_'label':_'previously_treated_doctor',_'type':_'text',_'required':_false}</t>
+          <t>previously_treated_doctor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'previously_treated_doctor', 'label': 'Previously Treated Doctor', 'type': 'text', 'required': False}</t>
+          <t>Previously Treated Doctor</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'medical_condition',_'label':_'medical_conditions',_'type':_'text',_'required':_false}</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'medical_condition', 'label': 'Medical Conditions', 'type': 'text', 'required': False}</t>
+          <t>Medical Conditions</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'result',_'label':_'result',_'type':_'select_one',_'options':_[{'name':_'positive',_'label':_'positive'},_{'name':_'negative',_'label':_'negative'},_{'name':_'unknown',_'label':_'unknown'}],_'required':_true}</t>
+          <t>result</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'result', 'label': 'Result', 'type': 'select_one', 'options': [{'name': 'Positive', 'label': 'Positive'}, {'name': 'Negative', 'label': 'Negative'}, {'name': 'Unknown', 'label': 'Unknown'}], 'required': True}</t>
+          <t>Result</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'reason',_'label':_'reason',_'type':_'text',_'required':_true}</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'reason', 'label': 'Reason', 'type': 'text', 'required': True}</t>
+          <t>Reason</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'screening_results',_'label':_'screening_results',_'type':_'select_multiple',_'required':_true,_'options':_[{'name':_'positive',_'label':_'positive'},_{'name':_'negative',_'label':_'negative'},_{'name':_'unknown',_'label':_'unknown'}]}</t>
+          <t>screening_results</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'screening_results', 'label': 'Screening Results', 'type': 'select_multiple', 'required': True, 'options': [{'name': 'Positive', 'label': 'Positive'}, {'name': 'Negative', 'label': 'Negative'}, {'name': 'Unknown', 'label': 'Unknown'}]}</t>
+          <t>Screening Results</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'name',_'label':_'name',_'type':_'text',_'required':_true}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'name', 'label': 'Name', 'type': 'text', 'required': True}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'label':_'phone',_'type':_'text',_'required':_true}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'phone', 'label': 'Phone', 'type': 'text', 'required': True}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'label':_'email',_'type':_'text',_'required':_true}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'email', 'label': 'Email', 'type': 'text', 'required': True}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'blood_pressure',_'label':_'blood_pressure',_'type':_'text',_'required':_false}</t>
+          <t>blood_pressure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'blood_pressure', 'label': 'Blood Pressure', 'type': 'text', 'required': False}</t>
+          <t>Blood Pressure</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'diabetes',_'label':_'diabetes',_'type':_'text',_'required':_false}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'diabetes', 'label': 'Diabetes', 'type': 'text', 'required': False}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'heart_disease',_'label':_'heart_disease',_'type':_'text',_'required':_false}</t>
+          <t>heart_disease</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'heart_disease', 'label': 'Heart Disease', 'type': 'text', 'required': False}</t>
+          <t>Heart Disease</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'kidney_disease',_'label':_'kidney_disease',_'type':_'text',_'required':_false}</t>
+          <t>kidney_disease</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'kidney_disease', 'label': 'Kidney Disease', 'type': 'text', 'required': False}</t>
+          <t>Kidney Disease</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'cancer',_'label':_'cancer',_'type':_'text',_'required':_false}</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'cancer', 'label': 'Cancer', 'type': 'text', 'required': False}</t>
+          <t>Cancer</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'epilepsy',_'label':_'epilepsy',_'type':_'text',_'required':_false}</t>
+          <t>epilepsy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'epilepsy', 'label': 'Epilepsy', 'type': 'text', 'required': False}</t>
+          <t>Epilepsy</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'other_medical_condition',_'label':_'other_medical_condition',_'type':_'text',_'required':_false}</t>
+          <t>other_medical_condition</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'other_medical_condition', 'label': 'Other Medical Condition', 'type': 'text', 'required': False}</t>
+          <t>Other Medical Condition</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'employee_name',_'label':_'name',_'type':_'text',_'required':_true}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'employee_name', 'label': 'Name', 'type': 'text', 'required': True}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'employee_id',_'label':_'employee_id',_'type':_'text',_'required':_true}</t>
+          <t>employee_id</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'employee_id', 'label': 'Employee ID', 'type': 'text', 'required': True}</t>
+          <t>Employee ID</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'employee_email',_'label':_'email',_'type':_'text',_'required':_true}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'employee_email', 'label': 'Email', 'type': 'text', 'required': True}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_'visitor_name',_'label':_'name',_'type':_'text',_'required':_true}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 'visitor_name', 'label': 'Name', 'type': 'text', 'required': True}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'name':_'contact_number',_'label':_'contact_number',_'type':_'text',_'required':_true}</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'name': 'contact_number', 'label': 'Contact Number', 'type': 'text', 'required': True}</t>
+          <t>Contact Number</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'label':_'email',_'type':_'text',_'required':_true}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'name': 'email', 'label': 'Email', 'type': 'text', 'required': True}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'name':_'contact_person',_'label':_'contact_person',_'type':_'text',_'required':_false}</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'name': 'contact_person', 'label': 'Contact Person', 'type': 'text', 'required': False}</t>
+          <t>Contact Person</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'name':_'medical_condition',_'label':_'medical_condition',_'type':_'text',_'required':_false}</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'name': 'medical_condition', 'label': 'Medical Condition', 'type': 'text', 'required': False}</t>
+          <t>Medical Condition</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'name':_'other_medical_condition',_'label':_'other_medical_condition',_'type':_'text',_'required':_false}</t>
+          <t>other_medical_condition</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'name': 'other_medical_condition', 'label': 'Other Medical Condition', 'type': 'text', 'required': False}</t>
+          <t>Other Medical Condition</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'name':_'recently_treated_doctor',_'label':_'recently_treated_doctor',_'type':_'text',_'required':_false}</t>
+          <t>recently_treated_doctor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'name': 'recently_treated_doctor', 'label': 'Recently Treated Doctor', 'type': 'text', 'required': False}</t>
+          <t>Recently Treated Doctor</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'name':_'visited_locations',_'label':_'visited_locations',_'type':_'text',_'required':_false}</t>
+          <t>visited_locations</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'name': 'visited_locations', 'label': 'Visited Locations', 'type': 'text', 'required': False}</t>
+          <t>Visited Locations</t>
         </is>
       </c>
     </row>
